--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">274862, 274863</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F6">
-        <v>756</v>
+        <v>349</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375541</t>
+          <t xml:space="preserve">274863</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F7">
-        <v>920</v>
+        <v>894</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375541</t>
+          <t xml:space="preserve">275237, 275238</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>330</v>
+        <v>2249</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375541</t>
+          <t xml:space="preserve">722445, 5375526</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>3165</v>
+        <v>501</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">722445, 5375526</t>
+          <t xml:space="preserve">722446, 2505065</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F10">
-        <v>501</v>
+        <v>315</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">722446, 2505065</t>
+          <t xml:space="preserve">7985807</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F11">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,30 +581,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">722448, 5375541</t>
+          <t xml:space="preserve">7967021</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F12">
-        <v>991</v>
+        <v>427</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200045178</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -636,25 +636,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F13">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200045178</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -681,30 +681,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967021</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F14">
-        <v>273</v>
+        <v>1178</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200048535</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -731,35 +731,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7985807</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F15">
-        <v>360</v>
+        <v>908</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311773086</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2034-07-12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">2504979</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -790,26 +790,26 @@
         </is>
       </c>
       <c r="F16">
-        <v>1042</v>
+        <v>530</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045747</t>
+          <t xml:space="preserve">311787238</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-17</t>
+          <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -831,35 +831,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">7104244</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>1671</v>
+        <v>416</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045747</t>
+          <t xml:space="preserve">311787240</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-17</t>
+          <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -881,35 +881,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F18">
-        <v>1178</v>
+        <v>1801</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048535</t>
+          <t xml:space="preserve">311823884</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-29</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>908</v>
+        <v>2211</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773086</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-12</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -981,25 +981,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2504979</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
-        <v>530</v>
+        <v>438</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787238</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-25</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1031,25 +1031,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104244</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787240</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-25</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">2502155</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F22">
-        <v>1801</v>
+        <v>1430</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823884</t>
+          <t xml:space="preserve">311831207</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F23">
-        <v>2211</v>
+        <v>1042</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831206</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F24">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831205</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F25">
-        <v>456</v>
+        <v>1671</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831206</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2502155</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F26">
-        <v>1430</v>
+        <v>1786</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831207</t>
+          <t xml:space="preserve">311831203</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1336,15 +1336,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F27">
-        <v>400</v>
+        <v>2248</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831205</t>
+          <t xml:space="preserve">311831204</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">5375372</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>1786</v>
+        <v>987</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831203</t>
+          <t xml:space="preserve">311831259</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">7985807</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>2248</v>
+        <v>540</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831204</t>
+          <t xml:space="preserve">311831201</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375372</t>
+          <t xml:space="preserve">2407326</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="F30">
-        <v>987</v>
+        <v>2236</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831259</t>
+          <t xml:space="preserve">311832241</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7985807</t>
+          <t xml:space="preserve">2407326</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F31">
-        <v>540</v>
+        <v>1376</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831201</t>
+          <t xml:space="preserve">311832241</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1581,25 +1581,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407326</t>
+          <t xml:space="preserve">2407325</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F32">
-        <v>2236</v>
+        <v>1600</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832241</t>
+          <t xml:space="preserve">311835556</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-16</t>
+          <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407326</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>1376</v>
+        <v>713</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832241</t>
+          <t xml:space="preserve">311835554</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-16</t>
+          <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407325</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="F34">
-        <v>1600</v>
+        <v>381</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835556</t>
+          <t xml:space="preserve">311835551</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1736,15 +1736,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>713</v>
+        <v>410</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835554</t>
+          <t xml:space="preserve">311835555</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1786,15 +1786,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36">
-        <v>381</v>
+        <v>493</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835551</t>
+          <t xml:space="preserve">311835553</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1831,20 +1831,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">5375601</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835555</t>
+          <t xml:space="preserve">311835581</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1881,20 +1881,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">5375601</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>493</v>
+        <v>402</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835553</t>
+          <t xml:space="preserve">311835581</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39">
-        <v>412</v>
+        <v>532</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375601</t>
+          <t xml:space="preserve">5376779</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>402</v>
+        <v>1051</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835581</t>
+          <t xml:space="preserve">311835549</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,20 +2031,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375601</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F41">
-        <v>532</v>
+        <v>285</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835581</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376779</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F42">
-        <v>1051</v>
+        <v>2250</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835549</t>
+          <t xml:space="preserve">311835560</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2136,15 +2136,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F43">
-        <v>285</v>
+        <v>805</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835562</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2186,15 +2186,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>2250</v>
+        <v>762</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835560</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2236,15 +2236,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F45">
-        <v>805</v>
+        <v>2095</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835562</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2286,15 +2286,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F46">
-        <v>762</v>
+        <v>1675</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835568</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2336,15 +2336,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F47">
-        <v>2095</v>
+        <v>543</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835564</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2386,15 +2386,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F48">
-        <v>1675</v>
+        <v>818</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835562</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">8234980</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>543</v>
+        <v>2246</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835564</t>
+          <t xml:space="preserve">311835548</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2481,20 +2481,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">8234980</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
-        <v>818</v>
+        <v>660</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835562</t>
+          <t xml:space="preserve">311835548</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51">
-        <v>2246</v>
+        <v>1483</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234980</t>
+          <t xml:space="preserve">7966463</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>660</v>
+        <v>765</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835548</t>
+          <t xml:space="preserve">311835942</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-02</t>
+          <t xml:space="preserve">2035-06-03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234980</t>
+          <t xml:space="preserve">100003854</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F53">
-        <v>1483</v>
+        <v>1025</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835548</t>
+          <t xml:space="preserve">311836245</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-02</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966463</t>
+          <t xml:space="preserve">2506048</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>765</v>
+        <v>1438</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835942</t>
+          <t xml:space="preserve">311836287</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-03</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003854</t>
+          <t xml:space="preserve">2506048</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="F55">
-        <v>1025</v>
+        <v>418</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836246</t>
+          <t xml:space="preserve">311836287</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506048</t>
+          <t xml:space="preserve">2507160</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="F56">
-        <v>1438</v>
+        <v>323</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836287</t>
+          <t xml:space="preserve">311836244</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,20 +2831,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506048</t>
+          <t xml:space="preserve">8174534</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>418</v>
+        <v>642</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836287</t>
+          <t xml:space="preserve">311836248</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2881,20 +2881,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2507160</t>
+          <t xml:space="preserve">9365846</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F58">
-        <v>323</v>
+        <v>718</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836244</t>
+          <t xml:space="preserve">311836288</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8174534</t>
+          <t xml:space="preserve">2400812</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836248</t>
+          <t xml:space="preserve">311836993</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9365846</t>
+          <t xml:space="preserve">2400822</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>718</v>
+        <v>1137</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836288</t>
+          <t xml:space="preserve">311836987</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400812</t>
+          <t xml:space="preserve">2479392</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="F61">
-        <v>580</v>
+        <v>655</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836993</t>
+          <t xml:space="preserve">311836994</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400822</t>
+          <t xml:space="preserve">2503062</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,11 +3090,11 @@
         </is>
       </c>
       <c r="F62">
-        <v>1137</v>
+        <v>369</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836987</t>
+          <t xml:space="preserve">311836998</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479392</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>655</v>
+        <v>1770</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836994</t>
+          <t xml:space="preserve">311837340</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-10</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503062</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F64">
-        <v>369</v>
+        <v>972</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836998</t>
+          <t xml:space="preserve">311837340</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-10</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3236,11 +3236,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>1770</v>
+        <v>1085</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3286,15 +3286,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F66">
-        <v>972</v>
+        <v>1095</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837340</t>
+          <t xml:space="preserve">311837342</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3336,11 +3336,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F67">
-        <v>1085</v>
+        <v>744</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3386,15 +3386,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F68">
-        <v>1095</v>
+        <v>1488</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837342</t>
+          <t xml:space="preserve">311837340</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3436,15 +3436,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F69">
-        <v>744</v>
+        <v>2518</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837340</t>
+          <t xml:space="preserve">311837339</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,20 +3481,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">2505547</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>1488</v>
+        <v>1312</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837340</t>
+          <t xml:space="preserve">311837295</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">2403979</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>2518</v>
+        <v>2179</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837339</t>
+          <t xml:space="preserve">311839035</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505547</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>1312</v>
+        <v>2711</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837295</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,20 +3631,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403979</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>2179</v>
+        <v>668</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839035</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74">
-        <v>2711</v>
+        <v>906</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839045</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3736,15 +3736,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F75">
-        <v>668</v>
+        <v>629</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839044</t>
+          <t xml:space="preserve">311839039</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">5375541</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F76">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839043</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">5375541</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>629</v>
+        <v>330</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839039</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112657</t>
+          <t xml:space="preserve">5375541</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78">
-        <v>829</v>
+        <v>3165</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843243</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404585</t>
+          <t xml:space="preserve">722448, 5375541</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F79">
-        <v>545</v>
+        <v>991</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843438</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479323</t>
+          <t xml:space="preserve">8112657</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>405</v>
+        <v>829</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843439</t>
+          <t xml:space="preserve">311843243</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,20 +4031,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479323</t>
+          <t xml:space="preserve">2404585</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>360</v>
+        <v>545</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843439</t>
+          <t xml:space="preserve">311843438</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4086,15 +4086,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>631</v>
+        <v>405</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843441</t>
+          <t xml:space="preserve">311843439</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4136,15 +4136,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>816</v>
+        <v>360</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843442</t>
+          <t xml:space="preserve">311843439</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9820080</t>
+          <t xml:space="preserve">2479323</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F84">
-        <v>462</v>
+        <v>631</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845342</t>
+          <t xml:space="preserve">311843441</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-18</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375189</t>
+          <t xml:space="preserve">2479323</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F85">
-        <v>7973</v>
+        <v>816</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845778</t>
+          <t xml:space="preserve">311843442</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-22</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375189</t>
+          <t xml:space="preserve">9820080</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>950</v>
+        <v>462</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845779</t>
+          <t xml:space="preserve">311845342</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-22</t>
+          <t xml:space="preserve">2035-07-18</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404714</t>
+          <t xml:space="preserve">5375189</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F87">
-        <v>396</v>
+        <v>7973</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846470</t>
+          <t xml:space="preserve">311845778</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-29</t>
+          <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">275237, 275238</t>
+          <t xml:space="preserve">5375189</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F88">
-        <v>2249</v>
+        <v>950</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846462</t>
+          <t xml:space="preserve">311845779</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-29</t>
+          <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,20 +4431,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376289</t>
+          <t xml:space="preserve">2404714</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F89">
-        <v>520</v>
+        <v>396</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846463</t>
+          <t xml:space="preserve">311846470</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,20 +4481,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9682559</t>
+          <t xml:space="preserve">5376289</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>905</v>
+        <v>520</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846468</t>
+          <t xml:space="preserve">311846463</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374749</t>
+          <t xml:space="preserve">9682559</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91">
-        <v>396</v>
+        <v>905</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855019</t>
+          <t xml:space="preserve">311846468</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-11</t>
+          <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407158</t>
+          <t xml:space="preserve">5374749</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>2195</v>
+        <v>396</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857899</t>
+          <t xml:space="preserve">311855017</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-24</t>
+          <t xml:space="preserve">2035-09-11</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407157</t>
+          <t xml:space="preserve">2407158</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4640,16 +4640,16 @@
         </is>
       </c>
       <c r="F93">
-        <v>1554</v>
+        <v>2195</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858506</t>
+          <t xml:space="preserve">311857899</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-26</t>
+          <t xml:space="preserve">2035-09-24</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407317</t>
+          <t xml:space="preserve">2407157</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,11 +4690,11 @@
         </is>
       </c>
       <c r="F94">
-        <v>343</v>
+        <v>1554</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858531</t>
+          <t xml:space="preserve">311858506</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4731,20 +4731,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407325</t>
+          <t xml:space="preserve">2407317</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>2253</v>
+        <v>343</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858397</t>
+          <t xml:space="preserve">311858531</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">274862, 274863</t>
+          <t xml:space="preserve">2407325</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F96">
-        <v>349</v>
+        <v>2253</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858520</t>
+          <t xml:space="preserve">311858397</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,20 +4831,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">274863</t>
+          <t xml:space="preserve">9409996</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>894</v>
+        <v>1349</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858520</t>
+          <t xml:space="preserve">311858534</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9409996</t>
+          <t xml:space="preserve">9745881</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>1349</v>
+        <v>1114</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858534</t>
+          <t xml:space="preserve">311865406</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-26</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9745881</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F99">
-        <v>1114</v>
+        <v>3698</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865406</t>
+          <t xml:space="preserve">311866773</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">5375493</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>1018</v>
+        <v>762</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866702</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F101">
-        <v>628</v>
+        <v>1803</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866540</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F102">
-        <v>814</v>
+        <v>1409</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F103">
-        <v>1428</v>
+        <v>650</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F104">
-        <v>1319</v>
+        <v>270</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F105">
-        <v>2104</v>
+        <v>873</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F106">
-        <v>629</v>
+        <v>1387</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5336,20 +5336,20 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>940</v>
+        <v>1018</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866531</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-05</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F108">
-        <v>3698</v>
+        <v>628</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866773</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375493</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F109">
-        <v>762</v>
+        <v>814</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866702</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F110">
-        <v>1803</v>
+        <v>756</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,20 +5531,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F111">
-        <v>1409</v>
+        <v>1428</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5581,20 +5581,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F112">
-        <v>650</v>
+        <v>1319</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5631,20 +5631,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F113">
-        <v>270</v>
+        <v>2104</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5681,20 +5681,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F114">
-        <v>873</v>
+        <v>629</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,11 +5740,11 @@
         </is>
       </c>
       <c r="F115">
-        <v>1387</v>
+        <v>940</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">

--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:L115"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1560</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>424</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1660</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>300</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">274862, 274863</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>349</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">274863</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>894</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringstedvej 129</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4173</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">275237, 275238</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>2249</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusvej 12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">722445, 5375526</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>501</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedevej 34</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">722446, 2505065</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>315</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">7985807</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>360</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksvej 29</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">7967021</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>427</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">200045178</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksvej 29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">7967021</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>273</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">200045178</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1178</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">200048535</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 47</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">38</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>908</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311773086</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-07-12</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skælskørvej 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2504979</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>530</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311787238</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 20</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104244</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>416</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311787240</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Omkørselsvejen 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>1801</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311823884</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>2211</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311823882</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>438</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311823882</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 19</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479795</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>456</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311823882</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fjenneslevmaglevej 23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4173</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2502155</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1430</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311831207</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505480</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1042</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311831206</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505480</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>400</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311831205</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505480</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1671</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311831206</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505480</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1786</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311831203</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505480</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>2248</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311831204</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongebrovej 7</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375372</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>987</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311831259</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Smedeparken 3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">7985807</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>540</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311831201</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ventemøllevej 32A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407326</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>2236</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311832241</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ventemøllevej 32B</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407326</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1376</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311832241</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ventemøllevej 30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407325</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>1600</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311835556</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1B</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505166</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>713</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311835554</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1C</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505166</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>381</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311835551</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505166</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>410</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311835555</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505166</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>493</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311835553</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 21</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375601</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>412</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311835581</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375601</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>402</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311835581</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375601</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>532</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311835581</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Abildvej 1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">5376779</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1051</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311835549</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>285</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311835565</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>2250</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311835560</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311835565</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>805</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311835562</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>762</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311835565</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>2095</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311835565</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>1675</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311835565</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>543</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311835564</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rustkammervej 76</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">7104238</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>818</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311835562</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">8234980</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>2246</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311835548</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tokesvej 3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">8234980</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>660</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311835548</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tokesvej 1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">8234980</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1483</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311835548</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krongårdsvej 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966463</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>765</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311835942</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-03</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Katrinelystvej 11C</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">100003854</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1025</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311836245</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311836246</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Veddevej 19A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4190</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2506048</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1438</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311836287</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Veddevej 19A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4190</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2506048</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>418</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311836287</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongevejen 7</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2507160</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>323</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311836244</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søholm 1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">8174534</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>642</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311836248</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sneppevej 4</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">9365846</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>718</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311836288</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongstedvej 20</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2400812</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>580</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311836993</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongstedvej 26</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2400822</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>1137</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311836987</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosenvænget 4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479392</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>655</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311836994</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Margrethevej 1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4173</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2503062</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>369</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311836998</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1770</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311837340</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>972</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311837340</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1085</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311837340</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 40</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>1095</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311837342</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>744</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311837340</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 50</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>1488</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311837340</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 48</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2406562</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>2518</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311837339</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lynge Byvej 54</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2505547</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>1312</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311837295</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovglimt 2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2403979</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>2179</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311839035</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 4</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375608</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>2711</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311839042</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311839045</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375608</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>668</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311839042</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311839044</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 6</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375608</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>906</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311839042</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311839043</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 7</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375608</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>629</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311839039</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringstedvej 20</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375541</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>920</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311842116</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringstedvej 20</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375541</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>330</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311842116</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringstedvej 20</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375541</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>3165</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311842116</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringstedvej 18</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">722448, 5375541</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>991</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311842116</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bjernedevej 27</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">8112657</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>829</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311843243</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 37</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404585</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>545</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311843438</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søparken 1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479323</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>405</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311843439</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søparken 1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479323</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>360</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311843439</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søparken 1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479323</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>631</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311843441</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søparken 1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4291</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2479323</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>816</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311843442</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thyrasvej 45</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4173</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">9820080</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>462</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311845342</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-18</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusvej 8</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375189</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>7973</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311845778</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusvej 6</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375189</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>950</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311845779</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404714</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>396</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311846470</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 10</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">5376289</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>520</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311846463</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Banevænget 8</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">9682559</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>905</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311846468</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storgade 7C</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374749</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>396</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311855017</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-11</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holbergsvej 63</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407158</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>2195</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311857899</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-24</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sømosevej 44</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407157</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>1554</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311858506</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundtoftevej 35</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407317</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>343</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311858531</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vibevej 7A</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2407325</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>2253</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311858397</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ventemøllevej 11</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4293</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">9409996</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>1349</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311858534</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pilevænget 1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">9745881</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>1114</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311865406</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 4</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>3698</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311866773</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frederiksvej 33</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">5375493</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>762</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311866702</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>1803</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 3</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>1409</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>650</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>270</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>873</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4295</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2404656</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>1387</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311866994</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>1018</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>628</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>814</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>756</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>1428</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>1319</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>2104</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>629</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,39 +6871,49 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alleen 8</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4180</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">5374910</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>940</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311866991</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
+  <autoFilter ref="A1:L115"/>
 </worksheet>
 </file>
--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 50</t>
+          <t xml:space="preserve">Rådhusvej 12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">722445, 5375526</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>1560</v>
+        <v>501</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 20</t>
+          <t xml:space="preserve">Skolegade 15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -166,11 +166,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H3">
-        <v>424</v>
+        <v>1660</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H4">
-        <v>1660</v>
+        <v>300</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15</t>
+          <t xml:space="preserve">Skolegade 20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -286,11 +286,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H5">
-        <v>300</v>
+        <v>424</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 2</t>
+          <t xml:space="preserve">Smedeparken 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">274862, 274863</t>
+          <t xml:space="preserve">7985807</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H6">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 3</t>
+          <t xml:space="preserve">Smedevej 34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">274863</t>
+          <t xml:space="preserve">722446, 2505065</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>894</v>
+        <v>315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 129</t>
+          <t xml:space="preserve">Sømosevej 50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">275237, 275238</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H8">
-        <v>2249</v>
+        <v>1560</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 12</t>
+          <t xml:space="preserve">Frederiksvej 29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,30 +521,30 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">722445, 5375526</t>
+          <t xml:space="preserve">7967021</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H9">
-        <v>501</v>
+        <v>427</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200045178</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedevej 34</t>
+          <t xml:space="preserve">Frederiksvej 29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,30 +581,30 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">722446, 2505065</t>
+          <t xml:space="preserve">7967021</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H10">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200045178</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -631,40 +631,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeparken 3</t>
+          <t xml:space="preserve">Sømosevej 50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7985807</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H11">
-        <v>360</v>
+        <v>1178</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200048535</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -691,45 +691,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 29</t>
+          <t xml:space="preserve">Sømosevej 47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967021</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="H12">
-        <v>427</v>
+        <v>908</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045178</t>
+          <t xml:space="preserve">311773086</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-03</t>
+          <t xml:space="preserve">2034-07-12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 29</t>
+          <t xml:space="preserve">Skælskørvej 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,35 +761,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7967021</t>
+          <t xml:space="preserve">2504979</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>273</v>
+        <v>530</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045178</t>
+          <t xml:space="preserve">311787238</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-03</t>
+          <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -811,45 +811,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 50</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">7104244</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>1178</v>
+        <v>416</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048535</t>
+          <t xml:space="preserve">311787240</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-29</t>
+          <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -871,35 +871,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 47</t>
+          <t xml:space="preserve">Omkørselsvejen 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H15">
-        <v>908</v>
+        <v>1801</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773086</t>
+          <t xml:space="preserve">311823884</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-12</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skælskørvej 1</t>
+          <t xml:space="preserve">Skolegade 19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2504979</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="H16">
-        <v>530</v>
+        <v>2211</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787238</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-25</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,35 +991,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Skolegade 19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104244</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787240</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-25</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,30 +1051,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omkørselsvejen 2</t>
+          <t xml:space="preserve">Skolegade 19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">2479795</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>1801</v>
+        <v>456</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823884</t>
+          <t xml:space="preserve">311823882</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1111,35 +1111,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 19</t>
+          <t xml:space="preserve">Fjenneslevmaglevej 23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4173</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">2502155</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H19">
-        <v>2211</v>
+        <v>1430</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831207</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,35 +1171,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 19</t>
+          <t xml:space="preserve">Kongebrovej 7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">5375372</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>438</v>
+        <v>987</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831259</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1231,35 +1231,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 19</t>
+          <t xml:space="preserve">Smedeparken 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479795</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>456</v>
+        <v>1042</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823882</t>
+          <t xml:space="preserve">311831206</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1291,30 +1291,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjenneslevmaglevej 23</t>
+          <t xml:space="preserve">Smedeparken 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2502155</t>
+          <t xml:space="preserve">2505480</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H22">
-        <v>1430</v>
+        <v>400</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831207</t>
+          <t xml:space="preserve">311831205</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1366,11 +1366,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H23">
-        <v>1042</v>
+        <v>1671</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1426,15 +1426,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H24">
-        <v>400</v>
+        <v>1786</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831205</t>
+          <t xml:space="preserve">311831203</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1486,15 +1486,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H25">
-        <v>1671</v>
+        <v>2248</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831206</t>
+          <t xml:space="preserve">311831204</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeparken 1</t>
+          <t xml:space="preserve">Smedeparken 3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,20 +1541,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">7985807</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>1786</v>
+        <v>540</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831203</t>
+          <t xml:space="preserve">311831201</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,35 +1591,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeparken 1</t>
+          <t xml:space="preserve">Ventemøllevej 32A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505480</t>
+          <t xml:space="preserve">2407326</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831204</t>
+          <t xml:space="preserve">311832241</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebrovej 7</t>
+          <t xml:space="preserve">Ventemøllevej 32B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375372</t>
+          <t xml:space="preserve">2407326</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>987</v>
+        <v>1376</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831259</t>
+          <t xml:space="preserve">311832241</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedeparken 3</t>
+          <t xml:space="preserve">Abildvej 1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7985807</t>
+          <t xml:space="preserve">5376779</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="H29">
-        <v>540</v>
+        <v>1051</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831201</t>
+          <t xml:space="preserve">311835549</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventemøllevej 32A</t>
+          <t xml:space="preserve">Holbergsvej 18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407326</t>
+          <t xml:space="preserve">8234980</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832241</t>
+          <t xml:space="preserve">311835548</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-16</t>
+          <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,35 +1831,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventemøllevej 32B</t>
+          <t xml:space="preserve">Holbergsvej 21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407326</t>
+          <t xml:space="preserve">5375601</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>1376</v>
+        <v>412</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832241</t>
+          <t xml:space="preserve">311835581</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-16</t>
+          <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventemøllevej 30</t>
+          <t xml:space="preserve">Holbergsvej 23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407325</t>
+          <t xml:space="preserve">5375601</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="H32">
-        <v>1600</v>
+        <v>402</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835556</t>
+          <t xml:space="preserve">311835581</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1B</t>
+          <t xml:space="preserve">Holbergsvej 25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">5375601</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H33">
-        <v>713</v>
+        <v>532</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835554</t>
+          <t xml:space="preserve">311835581</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1C</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,20 +2021,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H34">
-        <v>381</v>
+        <v>285</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835551</t>
+          <t xml:space="preserve">311835569</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1A</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H35">
-        <v>410</v>
+        <v>2250</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835555</t>
+          <t xml:space="preserve">311835560</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,20 +2141,20 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505166</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H36">
-        <v>493</v>
+        <v>805</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835553</t>
+          <t xml:space="preserve">311835562</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 21</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,20 +2201,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375601</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H37">
-        <v>412</v>
+        <v>762</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835581</t>
+          <t xml:space="preserve">311835568</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 23</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,20 +2261,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375601</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>402</v>
+        <v>2095</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835581</t>
+          <t xml:space="preserve">311835569</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 25</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,20 +2321,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375601</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H39">
-        <v>532</v>
+        <v>1675</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835581</t>
+          <t xml:space="preserve">311835569</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 1</t>
+          <t xml:space="preserve">Rustkammervej 76</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376779</t>
+          <t xml:space="preserve">7104238</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H40">
-        <v>1051</v>
+        <v>543</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835549</t>
+          <t xml:space="preserve">311835564</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2446,15 +2446,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H41">
-        <v>285</v>
+        <v>818</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835562</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Skolevej 1A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,20 +2501,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>2250</v>
+        <v>410</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835555</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Skolevej 1B</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,20 +2561,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>805</v>
+        <v>713</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835562</t>
+          <t xml:space="preserve">311835554</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Skolevej 1C</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,11 +2630,11 @@
         </is>
       </c>
       <c r="H44">
-        <v>762</v>
+        <v>381</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835551</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,20 +2681,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">2505166</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H45">
-        <v>2095</v>
+        <v>493</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835553</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Tokesvej 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">8234980</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H46">
-        <v>1675</v>
+        <v>1483</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835548</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Tokesvej 3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,20 +2801,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">8234980</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>543</v>
+        <v>660</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835564</t>
+          <t xml:space="preserve">311835548</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,30 +2851,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustkammervej 76</t>
+          <t xml:space="preserve">Ventemøllevej 30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7104238</t>
+          <t xml:space="preserve">2407325</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>818</v>
+        <v>1600</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835562</t>
+          <t xml:space="preserve">311835556</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 18</t>
+          <t xml:space="preserve">Krongårdsvej 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234980</t>
+          <t xml:space="preserve">7966463</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,16 +2930,16 @@
         </is>
       </c>
       <c r="H49">
-        <v>2246</v>
+        <v>765</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835548</t>
+          <t xml:space="preserve">311835942</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-02</t>
+          <t xml:space="preserve">2035-06-03</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tokesvej 3</t>
+          <t xml:space="preserve">Katrinelystvej 11C</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234980</t>
+          <t xml:space="preserve">100003854</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>660</v>
+        <v>1025</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835548</t>
+          <t xml:space="preserve">311836246</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-02</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tokesvej 1</t>
+          <t xml:space="preserve">Kongevejen 7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234980</t>
+          <t xml:space="preserve">2507160</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>1483</v>
+        <v>323</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835548</t>
+          <t xml:space="preserve">311836244</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-02</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krongårdsvej 2</t>
+          <t xml:space="preserve">Sneppevej 4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966463</t>
+          <t xml:space="preserve">9365846</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H52">
-        <v>765</v>
+        <v>718</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835942</t>
+          <t xml:space="preserve">311836288</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-03</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katrinelystvej 11C</t>
+          <t xml:space="preserve">Søholm 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,20 +3161,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003854</t>
+          <t xml:space="preserve">8174534</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>1025</v>
+        <v>642</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836246</t>
+          <t xml:space="preserve">311836248</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 7</t>
+          <t xml:space="preserve">Kongstedvej 20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2507160</t>
+          <t xml:space="preserve">2400812</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>323</v>
+        <v>580</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836244</t>
+          <t xml:space="preserve">311836993</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søholm 1</t>
+          <t xml:space="preserve">Kongstedvej 26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8174534</t>
+          <t xml:space="preserve">2400822</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>642</v>
+        <v>1137</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836248</t>
+          <t xml:space="preserve">311836987</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,35 +3451,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sneppevej 4</t>
+          <t xml:space="preserve">Margrethevej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4173</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9365846</t>
+          <t xml:space="preserve">2503062</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>718</v>
+        <v>369</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836288</t>
+          <t xml:space="preserve">311836998</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongstedvej 20</t>
+          <t xml:space="preserve">Rosenvænget 4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400812</t>
+          <t xml:space="preserve">2479392</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="H59">
-        <v>580</v>
+        <v>655</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836993</t>
+          <t xml:space="preserve">311836994</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongstedvej 26</t>
+          <t xml:space="preserve">Holbergsvej 40</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400822</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H60">
-        <v>1137</v>
+        <v>1095</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836987</t>
+          <t xml:space="preserve">311837342</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-10</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 4</t>
+          <t xml:space="preserve">Lynge Byvej 54</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479392</t>
+          <t xml:space="preserve">2505547</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,16 +3650,16 @@
         </is>
       </c>
       <c r="H61">
-        <v>655</v>
+        <v>1312</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836994</t>
+          <t xml:space="preserve">311837295</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-10</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 1</t>
+          <t xml:space="preserve">Sømosevej 48</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503062</t>
+          <t xml:space="preserve">2406562</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H62">
-        <v>369</v>
+        <v>2518</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836998</t>
+          <t xml:space="preserve">311837339</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-10</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 40</t>
+          <t xml:space="preserve">Sømosevej 50</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3946,15 +3946,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H66">
-        <v>1095</v>
+        <v>744</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837342</t>
+          <t xml:space="preserve">311837340</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4006,11 +4006,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H67">
-        <v>744</v>
+        <v>1488</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 50</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H68">
-        <v>1488</v>
+        <v>2711</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837340</t>
+          <t xml:space="preserve">311839045</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 48</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2406562</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H69">
-        <v>2518</v>
+        <v>668</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837339</t>
+          <t xml:space="preserve">311839044</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynge Byvej 54</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2505547</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H70">
-        <v>1312</v>
+        <v>906</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837295</t>
+          <t xml:space="preserve">311839043</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,30 +4231,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovglimt 2</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403979</t>
+          <t xml:space="preserve">5375608</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H71">
-        <v>2179</v>
+        <v>629</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839035</t>
+          <t xml:space="preserve">311839039</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 4</t>
+          <t xml:space="preserve">Skovglimt 2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">2403979</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,11 +4310,11 @@
         </is>
       </c>
       <c r="H72">
-        <v>2711</v>
+        <v>2179</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839045</t>
+          <t xml:space="preserve">311839035</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 5</t>
+          <t xml:space="preserve">Ringstedvej 18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">722448, 5375541</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H73">
-        <v>668</v>
+        <v>991</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839044</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 6</t>
+          <t xml:space="preserve">Ringstedvej 20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,25 +4421,25 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">5375541</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H74">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839043</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Kaarsbergsvej 7</t>
+          <t xml:space="preserve">Ringstedvej 20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375608</t>
+          <t xml:space="preserve">5375541</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H75">
-        <v>629</v>
+        <v>330</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839039</t>
+          <t xml:space="preserve">311842116</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4546,11 +4546,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76">
-        <v>920</v>
+        <v>3165</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 20</t>
+          <t xml:space="preserve">Bjernedevej 27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,25 +4601,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375541</t>
+          <t xml:space="preserve">8112657</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>330</v>
+        <v>829</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842116</t>
+          <t xml:space="preserve">311843243</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-01</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 20</t>
+          <t xml:space="preserve">Hovedgaden 37</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375541</t>
+          <t xml:space="preserve">2404585</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>3165</v>
+        <v>545</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842116</t>
+          <t xml:space="preserve">311843438</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-01</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,35 +4711,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 18</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">722448, 5375541</t>
+          <t xml:space="preserve">2479323</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>991</v>
+        <v>405</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842116</t>
+          <t xml:space="preserve">311843439</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-01</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjernedevej 27</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8112657</t>
+          <t xml:space="preserve">2479323</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H80">
-        <v>829</v>
+        <v>360</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843243</t>
+          <t xml:space="preserve">311843439</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,30 +4831,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 37</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4291</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404585</t>
+          <t xml:space="preserve">2479323</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H81">
-        <v>545</v>
+        <v>631</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843438</t>
+          <t xml:space="preserve">311843441</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4906,15 +4906,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H82">
-        <v>405</v>
+        <v>816</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843439</t>
+          <t xml:space="preserve">311843442</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Thyrasvej 45</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4173</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479323</t>
+          <t xml:space="preserve">9820080</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>360</v>
+        <v>462</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843439</t>
+          <t xml:space="preserve">311845342</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-07-18</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,35 +5011,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Rådhusvej 6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479323</t>
+          <t xml:space="preserve">5375189</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H84">
-        <v>631</v>
+        <v>950</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843441</t>
+          <t xml:space="preserve">311845779</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Rådhusvej 8</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2479323</t>
+          <t xml:space="preserve">5375189</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>816</v>
+        <v>7973</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843442</t>
+          <t xml:space="preserve">311845778</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-08</t>
+          <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,35 +5131,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thyrasvej 45</t>
+          <t xml:space="preserve">Banevænget 8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9820080</t>
+          <t xml:space="preserve">9682559</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H86">
-        <v>462</v>
+        <v>905</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845342</t>
+          <t xml:space="preserve">311846468</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-18</t>
+          <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 8</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375189</t>
+          <t xml:space="preserve">2404714</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H87">
-        <v>7973</v>
+        <v>396</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845778</t>
+          <t xml:space="preserve">311846470</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-22</t>
+          <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 6</t>
+          <t xml:space="preserve">Industrivej 10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,25 +5261,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375189</t>
+          <t xml:space="preserve">5376289</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>950</v>
+        <v>520</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845779</t>
+          <t xml:space="preserve">311846463</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-22</t>
+          <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,30 +5311,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Ringstedvej 129</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4173</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404714</t>
+          <t xml:space="preserve">275237, 275238</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>396</v>
+        <v>2249</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846470</t>
+          <t xml:space="preserve">311846462</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 10</t>
+          <t xml:space="preserve">Storgade 7C</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5376289</t>
+          <t xml:space="preserve">5374749</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H90">
-        <v>520</v>
+        <v>396</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846463</t>
+          <t xml:space="preserve">311855019</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-29</t>
+          <t xml:space="preserve">2035-09-11</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banevænget 8</t>
+          <t xml:space="preserve">Holbergsvej 63</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4293</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9682559</t>
+          <t xml:space="preserve">2407158</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>905</v>
+        <v>2195</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846468</t>
+          <t xml:space="preserve">311857899</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-29</t>
+          <t xml:space="preserve">2035-09-24</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storgade 7C</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374749</t>
+          <t xml:space="preserve">274862, 274863</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855017</t>
+          <t xml:space="preserve">311858520</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-11</t>
+          <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbergsvej 63</t>
+          <t xml:space="preserve">Dr. Kaarsbergsvej 3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407158</t>
+          <t xml:space="preserve">274863</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H93">
-        <v>2195</v>
+        <v>894</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857899</t>
+          <t xml:space="preserve">311858520</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-24</t>
+          <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sømosevej 44</t>
+          <t xml:space="preserve">Lundtoftevej 35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407157</t>
+          <t xml:space="preserve">2407317</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,11 +5630,11 @@
         </is>
       </c>
       <c r="H94">
-        <v>1554</v>
+        <v>343</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858506</t>
+          <t xml:space="preserve">311858531</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 35</t>
+          <t xml:space="preserve">Sømosevej 44</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407317</t>
+          <t xml:space="preserve">2407157</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,11 +5690,11 @@
         </is>
       </c>
       <c r="H95">
-        <v>343</v>
+        <v>1554</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858531</t>
+          <t xml:space="preserve">311858506</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibevej 7A</t>
+          <t xml:space="preserve">Ventemøllevej 11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,20 +5741,20 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2407325</t>
+          <t xml:space="preserve">9409996</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>2253</v>
+        <v>1349</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858397</t>
+          <t xml:space="preserve">311858534</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventemøllevej 11</t>
+          <t xml:space="preserve">Vibevej 7A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,20 +5801,20 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9409996</t>
+          <t xml:space="preserve">2407325</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H97">
-        <v>1349</v>
+        <v>2253</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858534</t>
+          <t xml:space="preserve">311858397</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5911,30 +5911,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 4</t>
+          <t xml:space="preserve">Frederiksvej 33</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5375493</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H99">
-        <v>3698</v>
+        <v>762</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866773</t>
+          <t xml:space="preserve">311866702</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,30 +5971,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 33</t>
+          <t xml:space="preserve">Idrætsvej 4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5375493</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H100">
-        <v>762</v>
+        <v>3698</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866702</t>
+          <t xml:space="preserve">311866773</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,11 +6050,11 @@
         </is>
       </c>
       <c r="H101">
-        <v>1803</v>
+        <v>1018</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6091,30 +6091,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 3</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H102">
-        <v>1409</v>
+        <v>628</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6170,11 +6170,11 @@
         </is>
       </c>
       <c r="H103">
-        <v>650</v>
+        <v>814</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,30 +6211,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H104">
-        <v>270</v>
+        <v>756</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,30 +6271,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H105">
-        <v>873</v>
+        <v>1428</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6331,30 +6331,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1</t>
+          <t xml:space="preserve">Alleen 8</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295</t>
+          <t xml:space="preserve">4180</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404656</t>
+          <t xml:space="preserve">5374910</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H106">
-        <v>1387</v>
+        <v>1319</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866994</t>
+          <t xml:space="preserve">311866991</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6406,11 +6406,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H107">
-        <v>1018</v>
+        <v>2104</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6466,11 +6466,11 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H108">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H109">
-        <v>814</v>
+        <v>940</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6571,30 +6571,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Hovedgaden 3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H110">
-        <v>756</v>
+        <v>1409</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,30 +6631,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Idrætsvej 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H111">
-        <v>1428</v>
+        <v>1803</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,30 +6691,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Idrætsvej 1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H112">
-        <v>1319</v>
+        <v>650</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6751,30 +6751,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Idrætsvej 1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H113">
-        <v>2104</v>
+        <v>270</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,30 +6811,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Idrætsvej 1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H114">
-        <v>629</v>
+        <v>873</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alleen 8</t>
+          <t xml:space="preserve">Idrætsvej 1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180</t>
+          <t xml:space="preserve">4295</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5374910</t>
+          <t xml:space="preserve">2404656</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>940</v>
+        <v>1387</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866991</t>
+          <t xml:space="preserve">311866994</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">

--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835568</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855019</t>
+          <t xml:space="preserve">311855017</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">

--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:M115"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-03</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-29</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">pch-consult ApS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-12</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-25</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-16</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2034,20 +2199,25 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2094,20 +2264,25 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835560</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2274,20 +2459,25 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2334,20 +2524,25 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835569</t>
+          <t xml:space="preserve">311835565</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-02</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-03</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-10</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-01</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-08</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-18</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-22</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-11</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-24</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-26</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,21 +7469,26 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-07</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L115"/>
+  <autoFilter ref="A1:M115"/>
 </worksheet>
 </file>
--- a/public/exports/29189994.xlsx
+++ b/public/exports/29189994.xlsx
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311835565</t>
+          <t xml:space="preserve">311835560</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836246</t>
+          <t xml:space="preserve">311836245</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839045</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839044</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4539,12 +4539,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839043</t>
+          <t xml:space="preserve">311839042</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K70" t="inlineStr">
